--- a/ProjectConfigTable/exgas_config/Datas/#exgas.asc.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.asc.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0C0DBA-8B48-498B-8B40-7C9503F5C395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0FF1416-CD16-4CDB-B452-7FB621AC99FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -93,9 +93,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>(list#sep=;),int</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -145,14 +142,29 @@
   </si>
   <si>
     <t>10002</t>
+  </si>
+  <si>
+    <t>level</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>(array#sep=;),int</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,6 +178,21 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -191,25 +218,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -487,17 +513,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.21875" customWidth="1" style="5"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1" style="5"/>
-    <col min="5" max="5" width="15.88671875" customWidth="1" style="3"/>
-    <col min="6" max="6" width="20.21875" customWidth="1" style="3"/>
-    <col min="7" max="7" width="20.6640625" customWidth="1" style="3"/>
+    <col min="3" max="3" width="16.21875" style="4" customWidth="1"/>
+    <col min="4" max="5" width="14.44140625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.21875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -511,16 +537,19 @@
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -533,181 +562,210 @@
       <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1002</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="3">
+        <v>1003</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="4">
-        <v>1003</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="G6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10">
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11">
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12">
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-    </row>
-    <row r="16">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-    </row>
-    <row r="17">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-    </row>
-    <row r="18">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-    </row>
-    <row r="19">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="6"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-    </row>
-    <row r="22">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="6"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
     </row>
-    <row r="25">
-      <c r="B25" s="6"/>
-    </row>
-    <row r="26">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="5"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.asc.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.asc.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -75,6 +75,9 @@
     <t>desc</t>
   </si>
   <si>
+    <t>level</t>
+  </si>
+  <si>
     <t>tag</t>
   </si>
   <si>
@@ -93,6 +96,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>(array#sep=;),int</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -102,6 +108,9 @@
     <t>描述</t>
   </si>
   <si>
+    <t>等级</t>
+  </si>
+  <si>
     <t>初始标签</t>
   </si>
   <si>
@@ -117,7 +126,7 @@
     <t>描述1</t>
   </si>
   <si>
-    <t>100;1001;1002</t>
+    <t>100;1001</t>
   </si>
   <si>
     <t>1</t>
@@ -142,29 +151,14 @@
   </si>
   <si>
     <t>10002</t>
-  </si>
-  <si>
-    <t>level</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>等级</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>(array#sep=;),int</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,21 +172,6 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -218,24 +197,25 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+  <cellXfs count="8">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -516,14 +496,14 @@
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.21875" style="4" customWidth="1"/>
-    <col min="4" max="5" width="14.44140625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.21875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="20.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" customWidth="1" style="5"/>
+    <col min="4" max="5" width="14.44140625" customWidth="1" style="5"/>
+    <col min="6" max="6" width="15.88671875" customWidth="1" style="3"/>
+    <col min="7" max="7" width="20.21875" customWidth="1" style="3"/>
+    <col min="8" max="8" width="20.6640625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -536,236 +516,237 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H1" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="6">
+        <v>19</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7">
         <v>0</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1002</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="4">
+        <v>1003</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="3">
-        <v>1003</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H6" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8">
       <c r="B8" s="1"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9">
       <c r="B9" s="1"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14">
       <c r="B14" s="1"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15">
       <c r="B15" s="1"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16">
       <c r="B16" s="1"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17">
       <c r="B17" s="1"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18">
       <c r="B18" s="1"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19">
       <c r="B19" s="1"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="6"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20">
       <c r="B20" s="1"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22">
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="B23" s="1"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="5"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25">
+      <c r="B25" s="6"/>
+    </row>
+    <row r="26">
       <c r="B26" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.asc.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.asc.xlsx
@@ -132,7 +132,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>10001;10002</t>
+    <t>10001;10002;1003;1005</t>
   </si>
   <si>
     <t>野怪1</t>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.asc.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.asc.xlsx
@@ -126,7 +126,7 @@
     <t>描述1</t>
   </si>
   <si>
-    <t>100;1001</t>
+    <t>100;1001;400</t>
   </si>
   <si>
     <t>1</t>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.asc.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.asc.xlsx
@@ -8,17 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0FF1416-CD16-4CDB-B452-7FB621AC99FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B3CB8F-4024-4DDB-86D5-8443C0518ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -61,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -126,9 +129,6 @@
     <t>描述1</t>
   </si>
   <si>
-    <t>100;1001;400</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -151,14 +151,17 @@
   </si>
   <si>
     <t>10002</t>
+  </si>
+  <si>
+    <t>1001;400</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,6 +175,21 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -197,25 +215,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -496,14 +513,14 @@
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.21875" customWidth="1" style="5"/>
-    <col min="4" max="5" width="14.44140625" customWidth="1" style="5"/>
-    <col min="6" max="6" width="15.88671875" customWidth="1" style="3"/>
-    <col min="7" max="7" width="20.21875" customWidth="1" style="3"/>
-    <col min="8" max="8" width="20.6640625" customWidth="1" style="3"/>
+    <col min="3" max="3" width="16.21875" style="4" customWidth="1"/>
+    <col min="4" max="5" width="14.44140625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.21875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -516,20 +533,20 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -542,20 +559,20 @@
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -568,20 +585,20 @@
       <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
@@ -589,164 +606,163 @@
       <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>0</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1002</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="3">
+        <v>1003</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="7">
+      <c r="D6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="4">
-        <v>1003</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="F6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="7">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10">
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-    </row>
-    <row r="11">
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7"/>
-    </row>
-    <row r="12">
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-    </row>
-    <row r="14">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-    </row>
-    <row r="15">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-    </row>
-    <row r="16">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-    </row>
-    <row r="17">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="7"/>
-    </row>
-    <row r="18">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="7"/>
-    </row>
-    <row r="19">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="7"/>
-    </row>
-    <row r="20">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="6"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="6"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
     </row>
-    <row r="25">
-      <c r="B25" s="6"/>
-    </row>
-    <row r="26">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="5"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.asc.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.asc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B3CB8F-4024-4DDB-86D5-8443C0518ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8782168-AA3C-4C64-835B-77118D1E7323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -72,24 +72,6 @@
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>tag</t>
-  </si>
-  <si>
-    <t>attrSet</t>
-  </si>
-  <si>
-    <t>ability</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -129,10 +111,13 @@
     <t>描述1</t>
   </si>
   <si>
+    <t>1001;400</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>10001;10002;1003;1005</t>
+    <t>10001;10002;20001</t>
   </si>
   <si>
     <t>野怪1</t>
@@ -153,7 +138,31 @@
     <t>10002</t>
   </si>
   <si>
-    <t>1001;400</t>
+    <t>ID</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tag</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttrSet</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ability</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -525,77 +534,77 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -604,22 +613,22 @@
         <v>1001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E4" s="6">
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -628,10 +637,10 @@
         <v>1002</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E5" s="6">
         <v>0</v>
@@ -642,22 +651,22 @@
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E6" s="6">
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
